--- a/exports/trend_1d/CGPOWER_full_report.xlsx
+++ b/exports/trend_1d/CGPOWER_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:U83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>10.39</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42038</v>
+        <v>42039</v>
       </c>
       <c r="H2" t="n">
-        <v>178.8</v>
+        <v>167.95</v>
       </c>
       <c r="I2" t="n">
         <v>178.48419884</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>-5.15</v>
+        <v>-10.9</v>
       </c>
       <c r="L2" t="n">
-        <v>6.05</v>
+        <v>12.44</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8</v>
+        <v>1.51</v>
       </c>
       <c r="N2" t="n">
-        <v>3.01</v>
+        <v>6.07</v>
       </c>
       <c r="O2" t="n">
         <v>1.86</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>13.8</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42054</v>
+        <v>42055</v>
       </c>
       <c r="H3" t="n">
-        <v>179.3</v>
+        <v>180.25</v>
       </c>
       <c r="I3" t="n">
         <v>179.8357280710206</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.76</v>
+        <v>-7.32</v>
       </c>
       <c r="L3" t="n">
-        <v>8.31</v>
+        <v>12.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1.16</v>
+        <v>4.35</v>
       </c>
       <c r="N3" t="n">
         <v>4.21</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.62</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42130</v>
+        <v>42131</v>
       </c>
       <c r="H4" t="n">
-        <v>165.7</v>
+        <v>161.35</v>
       </c>
       <c r="I4" t="n">
         <v>162.7054270906254</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K4" t="n">
-        <v>-8.07</v>
+        <v>-10.49</v>
       </c>
       <c r="L4" t="n">
         <v>13.7</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>11.44</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42192</v>
+        <v>42193</v>
       </c>
       <c r="H5" t="n">
-        <v>176.4</v>
+        <v>178.25</v>
       </c>
       <c r="I5" t="n">
         <v>177.2247328315815</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.33</v>
+        <v>-10.47</v>
       </c>
       <c r="L5" t="n">
-        <v>10.04</v>
+        <v>14.35</v>
       </c>
       <c r="M5" t="n">
         <v>1.27</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>9.43</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42209</v>
+        <v>42212</v>
       </c>
       <c r="H6" t="n">
-        <v>182.35</v>
+        <v>179.6</v>
       </c>
       <c r="I6" t="n">
         <v>180.8207500171904</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3</v>
+        <v>0.76</v>
       </c>
       <c r="L6" t="n">
         <v>2.33</v>
       </c>
       <c r="M6" t="n">
-        <v>1.38</v>
+        <v>2.63</v>
       </c>
       <c r="N6" t="n">
         <v>4.98</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>13.15</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42292</v>
+        <v>42293</v>
       </c>
       <c r="H7" t="n">
-        <v>181</v>
+        <v>189.6</v>
       </c>
       <c r="I7" t="n">
         <v>187.5448910053102</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.78</v>
+        <v>-5.57</v>
       </c>
       <c r="L7" t="n">
         <v>8.550000000000001</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>12.39</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42317</v>
+        <v>42318</v>
       </c>
       <c r="H8" t="n">
-        <v>168.95</v>
+        <v>167.15</v>
       </c>
       <c r="I8" t="n">
         <v>167.9772674804215</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>-10.89</v>
+        <v>-11.84</v>
       </c>
       <c r="L8" t="n">
         <v>13.42</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>10.94</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42327</v>
+        <v>42328</v>
       </c>
       <c r="H9" t="n">
-        <v>173.95</v>
+        <v>184.4</v>
       </c>
       <c r="I9" t="n">
         <v>183.9524260230379</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.07</v>
+        <v>-10.32</v>
       </c>
       <c r="L9" t="n">
-        <v>5.23</v>
+        <v>12.95</v>
       </c>
       <c r="M9" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>1.86</v>
+        <v>6.01</v>
       </c>
       <c r="O9" t="n">
         <v>-1.07</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>11.09</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42383</v>
+        <v>42384</v>
       </c>
       <c r="H10" t="n">
-        <v>180.4</v>
+        <v>176.4</v>
       </c>
       <c r="I10" t="n">
         <v>179.1510843048425</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.17</v>
+        <v>-4.34</v>
       </c>
       <c r="L10" t="n">
         <v>5.48</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>15.27</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42437</v>
+        <v>42438</v>
       </c>
       <c r="H11" t="n">
-        <v>139.45</v>
+        <v>151.85</v>
       </c>
       <c r="I11" t="n">
         <v>147.8988252847257</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K11" t="n">
-        <v>20.95</v>
+        <v>13.92</v>
       </c>
       <c r="L11" t="n">
         <v>3.91</v>
@@ -1068,7 +1199,7 @@
         <v>1.98</v>
       </c>
       <c r="N11" t="n">
-        <v>6.9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>-2.22</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>20.6</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42443</v>
+        <v>42444</v>
       </c>
       <c r="H12" t="n">
-        <v>155.3</v>
+        <v>44</v>
       </c>
       <c r="I12" t="n">
         <v>125.5032388155985</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>2.27</v>
+        <v>-71.02</v>
       </c>
       <c r="L12" t="n">
-        <v>7.61</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>65.87</v>
       </c>
       <c r="N12" t="n">
-        <v>2.76</v>
+        <v>71.67</v>
       </c>
       <c r="O12" t="n">
         <v>8.890000000000001</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>140.73</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42517</v>
+        <v>42520</v>
       </c>
       <c r="H13" t="n">
-        <v>60.15</v>
+        <v>68</v>
       </c>
       <c r="I13" t="n">
         <v>64.93306037020481</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K13" t="n">
-        <v>-36.7</v>
+        <v>-54.55</v>
       </c>
       <c r="L13" t="n">
-        <v>47.05</v>
+        <v>57.16</v>
       </c>
       <c r="M13" t="n">
         <v>3.63</v>
       </c>
       <c r="N13" t="n">
-        <v>6.48</v>
+        <v>13.05</v>
       </c>
       <c r="O13" t="n">
         <v>-71.67</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>17.12</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42625</v>
+        <v>42627</v>
       </c>
       <c r="H14" t="n">
-        <v>79.8</v>
+        <v>79.5</v>
       </c>
       <c r="I14" t="n">
         <v>79.56470053936856</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K14" t="n">
-        <v>17.35</v>
+        <v>16.91</v>
       </c>
       <c r="L14" t="n">
         <v>11.47</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>10.84</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42678</v>
+        <v>42681</v>
       </c>
       <c r="H15" t="n">
-        <v>77</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I15" t="n">
         <v>80.52069070495143</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K15" t="n">
-        <v>3.14</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>3.96</v>
+        <v>8.99</v>
       </c>
       <c r="M15" t="n">
         <v>1.73</v>
       </c>
       <c r="N15" t="n">
-        <v>4.93</v>
+        <v>11.56</v>
       </c>
       <c r="O15" t="n">
         <v>-0.38</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>15.32</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42689</v>
+        <v>42690</v>
       </c>
       <c r="H16" t="n">
-        <v>75.34999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="I16" t="n">
         <v>74.2134643474629</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K16" t="n">
-        <v>-12.28</v>
+        <v>-14.09</v>
       </c>
       <c r="L16" t="n">
         <v>17.87</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>18.97</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42746</v>
+        <v>42747</v>
       </c>
       <c r="H17" t="n">
-        <v>62.15</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>63.27781482256105</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K17" t="n">
-        <v>15.79</v>
+        <v>12.8</v>
       </c>
       <c r="L17" t="n">
         <v>7.38</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>9.31</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42780</v>
+        <v>42781</v>
       </c>
       <c r="H18" t="n">
-        <v>66.25</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I18" t="n">
         <v>65.69624534686199</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K18" t="n">
-        <v>2.95</v>
+        <v>0.85</v>
       </c>
       <c r="L18" t="n">
         <v>3.42</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="N18" t="n">
         <v>6.18</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>12.83</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42809</v>
+        <v>42810</v>
       </c>
       <c r="H19" t="n">
-        <v>69.90000000000001</v>
+        <v>73.55</v>
       </c>
       <c r="I19" t="n">
         <v>72.93076783513146</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K19" t="n">
-        <v>-7.7</v>
+        <v>-13.33</v>
       </c>
       <c r="L19" t="n">
-        <v>11.56</v>
+        <v>14.02</v>
       </c>
       <c r="M19" t="n">
         <v>4.14</v>
       </c>
       <c r="N19" t="n">
-        <v>3.65</v>
+        <v>5.22</v>
       </c>
       <c r="O19" t="n">
         <v>-2.04</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>12</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42881</v>
+        <v>42884</v>
       </c>
       <c r="H20" t="n">
-        <v>93.34999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I20" t="n">
         <v>84.24224191644174</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K20" t="n">
-        <v>26.92</v>
+        <v>7.27</v>
       </c>
       <c r="L20" t="n">
         <v>4.76</v>
       </c>
       <c r="M20" t="n">
-        <v>2.04</v>
+        <v>3.27</v>
       </c>
       <c r="N20" t="n">
-        <v>3.68</v>
+        <v>15.48</v>
       </c>
       <c r="O20" t="n">
         <v>5.22</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>26.61</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42982</v>
+        <v>42983</v>
       </c>
       <c r="H21" t="n">
-        <v>81.05</v>
+        <v>85.45</v>
       </c>
       <c r="I21" t="n">
         <v>81.91868147449189</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.72</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="L21" t="n">
         <v>14.64</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>12.68</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>42999</v>
+        <v>43000</v>
       </c>
       <c r="H22" t="n">
-        <v>82.09999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I22" t="n">
         <v>79.28387954006753</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.92</v>
+        <v>-7.43</v>
       </c>
       <c r="L22" t="n">
-        <v>6.26</v>
+        <v>7.72</v>
       </c>
       <c r="M22" t="n">
         <v>0.53</v>
       </c>
       <c r="N22" t="n">
-        <v>2.18</v>
+        <v>3.65</v>
       </c>
       <c r="O22" t="n">
         <v>5.43</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>11.98</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43039</v>
+        <v>43040</v>
       </c>
       <c r="H23" t="n">
-        <v>82.90000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>85.96046019302928</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.8</v>
+        <v>-9.48</v>
       </c>
       <c r="L23" t="n">
-        <v>7.46</v>
+        <v>10.37</v>
       </c>
       <c r="M23" t="n">
         <v>2.22</v>
       </c>
       <c r="N23" t="n">
-        <v>3.67</v>
+        <v>4.46</v>
       </c>
       <c r="O23" t="n">
         <v>-3.65</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>11.75</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H24" t="n">
-        <v>91.45</v>
+        <v>86</v>
       </c>
       <c r="I24" t="n">
         <v>89.11537515187042</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K24" t="n">
-        <v>5.6</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="L24" t="n">
         <v>9.35</v>
       </c>
       <c r="M24" t="n">
-        <v>1.67</v>
+        <v>2.46</v>
       </c>
       <c r="N24" t="n">
-        <v>3.68</v>
+        <v>5.96</v>
       </c>
       <c r="O24" t="n">
         <v>4.46</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>14.13</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43195</v>
+        <v>43196</v>
       </c>
       <c r="H25" t="n">
-        <v>80.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>81.87372380030875</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K25" t="n">
-        <v>6.63</v>
+        <v>4.53</v>
       </c>
       <c r="L25" t="n">
         <v>6.98</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>12.27</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43235</v>
+        <v>43236</v>
       </c>
       <c r="H26" t="n">
-        <v>77.45</v>
+        <v>76</v>
       </c>
       <c r="I26" t="n">
         <v>76.34571223139005</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.66</v>
+        <v>-7.43</v>
       </c>
       <c r="L26" t="n">
-        <v>6.27</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>1.1</v>
+        <v>1.81</v>
       </c>
       <c r="N26" t="n">
         <v>3.18</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.67</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43304</v>
+        <v>43305</v>
       </c>
       <c r="H27" t="n">
-        <v>60.85</v>
+        <v>63.7</v>
       </c>
       <c r="I27" t="n">
         <v>62.02317006258567</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K27" t="n">
-        <v>19.93</v>
+        <v>16.18</v>
       </c>
       <c r="L27" t="n">
         <v>5.26</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>21.25</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43353</v>
+        <v>43354</v>
       </c>
       <c r="H28" t="n">
-        <v>55.3</v>
+        <v>54</v>
       </c>
       <c r="I28" t="n">
         <v>54.84921598118538</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K28" t="n">
-        <v>-13.19</v>
+        <v>-15.23</v>
       </c>
       <c r="L28" t="n">
         <v>16.09</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>13.07</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43434</v>
+        <v>43437</v>
       </c>
       <c r="H29" t="n">
-        <v>38.75</v>
+        <v>41.1</v>
       </c>
       <c r="I29" t="n">
         <v>40.22837695593194</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K29" t="n">
-        <v>28.24</v>
+        <v>23.89</v>
       </c>
       <c r="L29" t="n">
         <v>3.61</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>17.49</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43488</v>
+        <v>43489</v>
       </c>
       <c r="H30" t="n">
-        <v>40.5</v>
+        <v>38.7</v>
       </c>
       <c r="I30" t="n">
         <v>40.11341879502999</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.46</v>
+        <v>-5.84</v>
       </c>
       <c r="L30" t="n">
         <v>12.17</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>15.22</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43524</v>
+        <v>43525</v>
       </c>
       <c r="H31" t="n">
-        <v>32.2</v>
+        <v>36.6</v>
       </c>
       <c r="I31" t="n">
         <v>36.32794998239223</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K31" t="n">
-        <v>16.8</v>
+        <v>5.43</v>
       </c>
       <c r="L31" t="n">
         <v>4.65</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>29.21</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43571</v>
+        <v>43573</v>
       </c>
       <c r="H32" t="n">
-        <v>38.65</v>
+        <v>36.9</v>
       </c>
       <c r="I32" t="n">
         <v>37.71522998722517</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K32" t="n">
-        <v>5.6</v>
+        <v>0.82</v>
       </c>
       <c r="L32" t="n">
         <v>11.34</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>17.39</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43713</v>
+        <v>43714</v>
       </c>
       <c r="H33" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="I33" t="n">
         <v>12.6406095056748</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K33" t="n">
-        <v>67.20999999999999</v>
+        <v>65.58</v>
       </c>
       <c r="L33" t="n">
         <v>12.74</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>21.31</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43748</v>
+        <v>43749</v>
       </c>
       <c r="H34" t="n">
-        <v>13.85</v>
+        <v>13.25</v>
       </c>
       <c r="I34" t="n">
         <v>13.31199920624645</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K34" t="n">
-        <v>9.06</v>
+        <v>4.33</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>20.87</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43774</v>
+        <v>43775</v>
       </c>
       <c r="H35" t="n">
-        <v>15.25</v>
+        <v>16</v>
       </c>
       <c r="I35" t="n">
         <v>15.87397843552105</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K35" t="n">
-        <v>-15.09</v>
+        <v>-20.75</v>
       </c>
       <c r="L35" t="n">
-        <v>15.09</v>
+        <v>20.75</v>
       </c>
       <c r="M35" t="n">
-        <v>4.86</v>
+        <v>4.92</v>
       </c>
       <c r="N35" t="n">
         <v>4.96</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>14.48</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43787</v>
+        <v>43788</v>
       </c>
       <c r="H36" t="n">
-        <v>14.95</v>
+        <v>14.5</v>
       </c>
       <c r="I36" t="n">
         <v>14.65439238087244</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K36" t="n">
-        <v>-6.56</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>8.130000000000001</v>
+        <v>10.62</v>
       </c>
       <c r="M36" t="n">
         <v>1.84</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>19.38</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43854</v>
+        <v>43857</v>
       </c>
       <c r="H37" t="n">
-        <v>9.25</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I37" t="n">
         <v>9.593980369592318</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K37" t="n">
-        <v>36.21</v>
+        <v>33.1</v>
       </c>
       <c r="L37" t="n">
         <v>3.79</v>
       </c>
       <c r="M37" t="n">
-        <v>4.73</v>
+        <v>4.86</v>
       </c>
       <c r="N37" t="n">
         <v>4.97</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>18.07</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43862</v>
+        <v>43864</v>
       </c>
       <c r="H38" t="n">
-        <v>9.15</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I38" t="n">
         <v>8.90161733556314</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K38" t="n">
-        <v>-5.67</v>
+        <v>-10.31</v>
       </c>
       <c r="L38" t="n">
-        <v>5.67</v>
+        <v>10.31</v>
       </c>
       <c r="M38" t="n">
         <v>4.95</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>17.74</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43929</v>
+        <v>43930</v>
       </c>
       <c r="H39" t="n">
-        <v>6.05</v>
+        <v>6.65</v>
       </c>
       <c r="I39" t="n">
         <v>6.113548592261916</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K39" t="n">
-        <v>30.46</v>
+        <v>23.56</v>
       </c>
       <c r="L39" t="n">
         <v>14.37</v>
       </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>9.92</v>
       </c>
       <c r="N39" t="n">
-        <v>4.95</v>
+        <v>9.92</v>
       </c>
       <c r="O39" t="n">
         <v>-4.92</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>15.64</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43956</v>
+        <v>43957</v>
       </c>
       <c r="H40" t="n">
-        <v>7.25</v>
+        <v>7.05</v>
       </c>
       <c r="I40" t="n">
         <v>7.174782612289586</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K40" t="n">
-        <v>9.02</v>
+        <v>6.02</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>21.8</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>43994</v>
+        <v>43997</v>
       </c>
       <c r="H41" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="I41" t="n">
         <v>6.734415567127887</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K41" t="n">
-        <v>7.8</v>
+        <v>4.26</v>
       </c>
       <c r="L41" t="n">
         <v>8.51</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>18.37</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44022</v>
+        <v>44025</v>
       </c>
       <c r="H42" t="n">
-        <v>9.300000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="I42" t="n">
         <v>9.117178924833716</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K42" t="n">
-        <v>37.78</v>
+        <v>31.11</v>
       </c>
       <c r="L42" t="n">
         <v>5.19</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>16.51</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44043</v>
+        <v>44046</v>
       </c>
       <c r="H43" t="n">
-        <v>9.300000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="I43" t="n">
         <v>9.475500276337371</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.08</v>
+        <v>-10.17</v>
       </c>
       <c r="L43" t="n">
-        <v>5.08</v>
+        <v>10.17</v>
       </c>
       <c r="M43" t="n">
-        <v>4.49</v>
+        <v>4.84</v>
       </c>
       <c r="N43" t="n">
-        <v>4.71</v>
+        <v>4.84</v>
       </c>
       <c r="O43" t="n">
         <v>-4.84</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>14.21</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44176</v>
+        <v>44179</v>
       </c>
       <c r="H44" t="n">
-        <v>44.6</v>
+        <v>42.4</v>
       </c>
       <c r="I44" t="n">
         <v>43.61907549548147</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K44" t="n">
-        <v>357.44</v>
+        <v>334.87</v>
       </c>
       <c r="L44" t="n">
         <v>0.51</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>22.97</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44235</v>
+        <v>44236</v>
       </c>
       <c r="H45" t="n">
-        <v>44.7</v>
+        <v>46.9</v>
       </c>
       <c r="I45" t="n">
         <v>46.0234967680085</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.42</v>
+        <v>-10.61</v>
       </c>
       <c r="L45" t="n">
         <v>12.03</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>13.26</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44302</v>
+        <v>44305</v>
       </c>
       <c r="H46" t="n">
-        <v>71.8</v>
+        <v>68.3</v>
       </c>
       <c r="I46" t="n">
         <v>68.3187000363112</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K46" t="n">
-        <v>53.09</v>
+        <v>45.63</v>
       </c>
       <c r="L46" t="n">
         <v>6.18</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>17.41</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44320</v>
+        <v>44321</v>
       </c>
       <c r="H47" t="n">
-        <v>76.55</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="I47" t="n">
         <v>77.18193279810248</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K47" t="n">
-        <v>-12.08</v>
+        <v>-17.64</v>
       </c>
       <c r="L47" t="n">
-        <v>12.3</v>
+        <v>17.64</v>
       </c>
       <c r="M47" t="n">
         <v>5</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>14.26</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44385</v>
+        <v>44386</v>
       </c>
       <c r="H48" t="n">
-        <v>78</v>
+        <v>77.8</v>
       </c>
       <c r="I48" t="n">
         <v>77.98467666232119</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.92</v>
+        <v>-3.17</v>
       </c>
       <c r="L48" t="n">
         <v>5.41</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>11.55</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44411</v>
+        <v>44412</v>
       </c>
       <c r="H49" t="n">
-        <v>83.05</v>
+        <v>87.2</v>
       </c>
       <c r="I49" t="n">
         <v>83.59661694258554</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>-6.75</v>
+        <v>-12.08</v>
       </c>
       <c r="L49" t="n">
-        <v>6.75</v>
+        <v>12.08</v>
       </c>
       <c r="M49" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="N49" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="O49" t="n">
         <v>-0.26</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>11.08</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44418</v>
+        <v>44419</v>
       </c>
       <c r="H50" t="n">
-        <v>77.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="I50" t="n">
         <v>77.53966632232954</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K50" t="n">
-        <v>-10.67</v>
+        <v>-13.42</v>
       </c>
       <c r="L50" t="n">
-        <v>10.67</v>
+        <v>15.08</v>
       </c>
       <c r="M50" t="n">
-        <v>0.06</v>
+        <v>3.53</v>
       </c>
       <c r="N50" t="n">
         <v>5</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>14.92</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44440</v>
+        <v>44441</v>
       </c>
       <c r="H51" t="n">
-        <v>85.8</v>
+        <v>90.05</v>
       </c>
       <c r="I51" t="n">
         <v>86.76837043332762</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K51" t="n">
-        <v>-13.64</v>
+        <v>-19.27</v>
       </c>
       <c r="L51" t="n">
-        <v>15.1</v>
+        <v>19.27</v>
       </c>
       <c r="M51" t="n">
         <v>2.52</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>13.05</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44579</v>
+        <v>44580</v>
       </c>
       <c r="H52" t="n">
-        <v>181.4</v>
+        <v>180.6</v>
       </c>
       <c r="I52" t="n">
         <v>180.895353470309</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K52" t="n">
-        <v>101.44</v>
+        <v>100.56</v>
       </c>
       <c r="L52" t="n">
         <v>5.77</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>5</v>
+      </c>
+      <c r="U52" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>13.37</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44643</v>
+        <v>44644</v>
       </c>
       <c r="H53" t="n">
-        <v>178.5</v>
+        <v>183.4</v>
       </c>
       <c r="I53" t="n">
         <v>182.6850157384595</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K53" t="n">
-        <v>1.16</v>
+        <v>-1.55</v>
       </c>
       <c r="L53" t="n">
         <v>5.51</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>12.78</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44673</v>
+        <v>44676</v>
       </c>
       <c r="H54" t="n">
-        <v>193.1</v>
+        <v>187.2</v>
       </c>
       <c r="I54" t="n">
         <v>187.6525247319953</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K54" t="n">
-        <v>5.29</v>
+        <v>2.07</v>
       </c>
       <c r="L54" t="n">
         <v>3.33</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>14.14</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44735</v>
+        <v>44736</v>
       </c>
       <c r="H55" t="n">
-        <v>181.4</v>
+        <v>186.2</v>
       </c>
       <c r="I55" t="n">
         <v>186.063610304164</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K55" t="n">
-        <v>3.1</v>
+        <v>0.53</v>
       </c>
       <c r="L55" t="n">
         <v>9.460000000000001</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>11.33</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44809</v>
+        <v>44810</v>
       </c>
       <c r="H56" t="n">
-        <v>219.7</v>
+        <v>215.25</v>
       </c>
       <c r="I56" t="n">
         <v>218.2143168522194</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K56" t="n">
-        <v>17.99</v>
+        <v>15.6</v>
       </c>
       <c r="L56" t="n">
         <v>2.31</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>11.01</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44820</v>
+        <v>44823</v>
       </c>
       <c r="H57" t="n">
-        <v>236</v>
+        <v>240.05</v>
       </c>
       <c r="I57" t="n">
         <v>238.8868395964544</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K57" t="n">
-        <v>-9.640000000000001</v>
+        <v>-11.52</v>
       </c>
       <c r="L57" t="n">
         <v>12.2</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>10.08</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44834</v>
+        <v>44837</v>
       </c>
       <c r="H58" t="n">
-        <v>235.7</v>
+        <v>229.6</v>
       </c>
       <c r="I58" t="n">
         <v>233.2949533485618</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.81</v>
+        <v>-4.35</v>
       </c>
       <c r="L58" t="n">
-        <v>3.56</v>
+        <v>6.44</v>
       </c>
       <c r="M58" t="n">
         <v>1.59</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>13.18</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44851</v>
+        <v>44852</v>
       </c>
       <c r="H59" t="n">
-        <v>254.25</v>
+        <v>260.5</v>
       </c>
       <c r="I59" t="n">
         <v>259.121358793418</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K59" t="n">
-        <v>-10.74</v>
+        <v>-13.46</v>
       </c>
       <c r="L59" t="n">
         <v>14.72</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>12.06</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44915</v>
+        <v>44916</v>
       </c>
       <c r="H60" t="n">
-        <v>269.55</v>
+        <v>262.6</v>
       </c>
       <c r="I60" t="n">
         <v>264.3198223307679</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K60" t="n">
-        <v>3.47</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L60" t="n">
         <v>5.53</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>44932</v>
+        <v>44935</v>
       </c>
       <c r="H61" t="n">
-        <v>270</v>
+        <v>289.45</v>
       </c>
       <c r="I61" t="n">
         <v>275.6946358723287</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.82</v>
+        <v>-10.22</v>
       </c>
       <c r="L61" t="n">
-        <v>5.52</v>
+        <v>10.97</v>
       </c>
       <c r="M61" t="n">
         <v>1.98</v>
       </c>
       <c r="N61" t="n">
-        <v>2.67</v>
+        <v>7.2</v>
       </c>
       <c r="O61" t="n">
         <v>-2.58</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>11.75</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>44984</v>
+        <v>44985</v>
       </c>
       <c r="H62" t="n">
-        <v>310.9</v>
+        <v>305.25</v>
       </c>
       <c r="I62" t="n">
         <v>305.8984269811792</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K62" t="n">
-        <v>7.41</v>
+        <v>5.46</v>
       </c>
       <c r="L62" t="n">
         <v>6.34</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>11.76</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45054</v>
+        <v>45055</v>
       </c>
       <c r="H63" t="n">
-        <v>312.35</v>
+        <v>320.5</v>
       </c>
       <c r="I63" t="n">
         <v>316.5176040011805</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.33</v>
+        <v>-5</v>
       </c>
       <c r="L63" t="n">
-        <v>4.44</v>
+        <v>5.95</v>
       </c>
       <c r="M63" t="n">
         <v>1.32</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>10.65</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45205</v>
+        <v>45208</v>
       </c>
       <c r="H64" t="n">
-        <v>418.75</v>
+        <v>413.25</v>
       </c>
       <c r="I64" t="n">
         <v>416.3827574360425</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K64" t="n">
-        <v>30.66</v>
+        <v>28.94</v>
       </c>
       <c r="L64" t="n">
         <v>3.49</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>6</v>
+      </c>
+      <c r="U64" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>10</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45251</v>
+        <v>45252</v>
       </c>
       <c r="H65" t="n">
-        <v>391.15</v>
+        <v>469.35</v>
       </c>
       <c r="I65" t="n">
         <v>416.5907253458926</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K65" t="n">
-        <v>5.35</v>
+        <v>-13.58</v>
       </c>
       <c r="L65" t="n">
-        <v>1.52</v>
+        <v>13.58</v>
       </c>
       <c r="M65" t="n">
         <v>1.5</v>
       </c>
       <c r="N65" t="n">
-        <v>3.64</v>
+        <v>19.99</v>
       </c>
       <c r="O65" t="n">
         <v>-1.31</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>21.41</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="H66" t="n">
-        <v>438.6</v>
+        <v>430.1</v>
       </c>
       <c r="I66" t="n">
         <v>430.4301445191655</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K66" t="n">
-        <v>-6.55</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="L66" t="n">
         <v>17.76</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>11.62</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="H67" t="n">
-        <v>465</v>
+        <v>472.85</v>
       </c>
       <c r="I67" t="n">
         <v>469.6665958294767</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K67" t="n">
-        <v>-8.109999999999999</v>
+        <v>-9.94</v>
       </c>
       <c r="L67" t="n">
         <v>15.08</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>12.13</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45489</v>
+        <v>45491</v>
       </c>
       <c r="H68" t="n">
-        <v>730.6</v>
+        <v>689.3</v>
       </c>
       <c r="I68" t="n">
         <v>691.4819807416845</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K68" t="n">
-        <v>54.51</v>
+        <v>45.78</v>
       </c>
       <c r="L68" t="n">
         <v>4.96</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>5</v>
+      </c>
+      <c r="U68" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>14.48</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45552</v>
+        <v>45553</v>
       </c>
       <c r="H69" t="n">
-        <v>731.1</v>
+        <v>743.25</v>
       </c>
       <c r="I69" t="n">
         <v>731.6181739318804</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K69" t="n">
-        <v>-6.06</v>
+        <v>-7.83</v>
       </c>
       <c r="L69" t="n">
         <v>10.97</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>10.28</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45586</v>
+        <v>45587</v>
       </c>
       <c r="H70" t="n">
-        <v>775.6</v>
+        <v>755.2</v>
       </c>
       <c r="I70" t="n">
         <v>763.0370634500011</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K70" t="n">
-        <v>4.35</v>
+        <v>1.61</v>
       </c>
       <c r="L70" t="n">
         <v>4.6</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>19.64</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45631</v>
+        <v>45632</v>
       </c>
       <c r="H71" t="n">
-        <v>769.35</v>
+        <v>782.5</v>
       </c>
       <c r="I71" t="n">
         <v>778.8123676319171</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K71" t="n">
-        <v>-1.87</v>
+        <v>-3.61</v>
       </c>
       <c r="L71" t="n">
         <v>8.859999999999999</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>10.39</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="H72" t="n">
-        <v>727.6</v>
+        <v>713.7</v>
       </c>
       <c r="I72" t="n">
         <v>721.3643018760242</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K72" t="n">
-        <v>-7.02</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L72" t="n">
-        <v>8.369999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M72" t="n">
         <v>2.18</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>10.55</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H73" t="n">
-        <v>635.15</v>
+        <v>663.3</v>
       </c>
       <c r="I73" t="n">
         <v>655.1809210658081</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K73" t="n">
-        <v>11.01</v>
+        <v>7.06</v>
       </c>
       <c r="L73" t="n">
         <v>5.6</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>4</v>
+      </c>
+      <c r="U73" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>14.86</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45750</v>
+        <v>45751</v>
       </c>
       <c r="H74" t="n">
-        <v>615.95</v>
+        <v>575.2</v>
       </c>
       <c r="I74" t="n">
         <v>575.5396637007711</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K74" t="n">
-        <v>-7.14</v>
+        <v>-13.28</v>
       </c>
       <c r="L74" t="n">
-        <v>8.529999999999999</v>
+        <v>13.95</v>
       </c>
       <c r="M74" t="n">
         <v>0.9</v>
       </c>
       <c r="N74" t="n">
-        <v>3.68</v>
+        <v>6.62</v>
       </c>
       <c r="O74" t="n">
         <v>4.43</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>17.56</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="H75" t="n">
-        <v>619.85</v>
+        <v>650.6</v>
       </c>
       <c r="I75" t="n">
         <v>626.940707761487</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K75" t="n">
-        <v>-7.76</v>
+        <v>-13.11</v>
       </c>
       <c r="L75" t="n">
-        <v>8.300000000000001</v>
+        <v>13.45</v>
       </c>
       <c r="M75" t="n">
         <v>3.06</v>
       </c>
       <c r="N75" t="n">
-        <v>3.88</v>
+        <v>4.96</v>
       </c>
       <c r="O75" t="n">
         <v>-6.62</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S75" t="b">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>14.04</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H76" t="n">
-        <v>759.1</v>
+        <v>739.4</v>
       </c>
       <c r="I76" t="n">
         <v>742.5266210423636</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K76" t="n">
-        <v>16.68</v>
+        <v>13.65</v>
       </c>
       <c r="L76" t="n">
         <v>11.16</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>6</v>
+      </c>
+      <c r="U76" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="77">
@@ -4809,25 +5732,25 @@
         <v>7.93</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H77" t="n">
-        <v>608.35</v>
+        <v>661.55</v>
       </c>
       <c r="I77" t="n">
         <v>609.2196999058791</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K77" t="n">
-        <v>17.72</v>
+        <v>10.53</v>
       </c>
       <c r="L77" t="n">
         <v>3.94</v>
       </c>
       <c r="M77" t="n">
-        <v>3.26</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="N77" t="n">
         <v>9.67</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>6</v>
+      </c>
+      <c r="U77" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="78">
@@ -4866,22 +5801,22 @@
         <v>14.62</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="H78" t="n">
-        <v>681.6</v>
+        <v>664.1</v>
       </c>
       <c r="I78" t="n">
         <v>666.3939894581004</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K78" t="n">
-        <v>3.03</v>
+        <v>0.39</v>
       </c>
       <c r="L78" t="n">
-        <v>1.62</v>
+        <v>2.83</v>
       </c>
       <c r="M78" t="n">
         <v>5</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>11.37</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H79" t="n">
-        <v>716.1</v>
+        <v>748</v>
       </c>
       <c r="I79" t="n">
         <v>739.616445474065</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K79" t="n">
-        <v>-7.83</v>
+        <v>-12.63</v>
       </c>
       <c r="L79" t="n">
-        <v>10.77</v>
+        <v>12.93</v>
       </c>
       <c r="M79" t="n">
         <v>3.06</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>11.73</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="H80" t="n">
-        <v>912.85</v>
+        <v>883.8</v>
       </c>
       <c r="I80" t="n">
         <v>887.1620100726625</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K80" t="n">
-        <v>22.04</v>
+        <v>18.16</v>
       </c>
       <c r="L80" t="n">
         <v>2.87</v>
@@ -5010,7 +5969,19 @@
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>4</v>
+      </c>
+      <c r="U80" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -5037,22 +6008,22 @@
         <v>10.62</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="H81" t="n">
-        <v>889</v>
+        <v>916</v>
       </c>
       <c r="I81" t="n">
         <v>909.7536702842748</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.59</v>
+        <v>-3.64</v>
       </c>
       <c r="L81" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="M81" t="n">
         <v>2.48</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -5094,22 +6077,22 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="H82" t="n">
-        <v>858</v>
+        <v>851.55</v>
       </c>
       <c r="I82" t="n">
         <v>854.587219028603</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K82" t="n">
-        <v>-6.33</v>
+        <v>-7.04</v>
       </c>
       <c r="L82" t="n">
-        <v>6.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M82" t="n">
         <v>1.53</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S82" t="b">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -5175,6 +6170,14 @@
       <c r="Q83" t="n">
         <v>29</v>
       </c>
+      <c r="R83" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10133,7 +11136,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51.1</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="6">
@@ -10143,7 +11146,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -10153,7 +11156,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8">
@@ -10163,7 +11166,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -10173,7 +11176,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -10183,7 +11186,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
@@ -10193,7 +11196,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -10203,7 +11206,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -10213,7 +11216,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>37</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="14">
@@ -10223,7 +11226,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.65</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="15">
@@ -10233,7 +11236,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.56</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="16">
@@ -10243,7 +11246,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.57</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="17">
@@ -10253,7 +11256,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>357.44</v>
+        <v>334.87</v>
       </c>
     </row>
     <row r="18">
@@ -10263,7 +11266,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -10273,7 +11276,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.16</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="20">
@@ -10283,7 +11286,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.34</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="21">
@@ -10293,7 +11296,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>47.05</v>
+        <v>73.45999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -10303,7 +11306,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23">
@@ -10313,7 +11316,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
@@ -10323,7 +11326,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.98</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="25">
@@ -10333,7 +11336,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.949999999999999</v>
+        <v>65.87</v>
       </c>
     </row>
     <row r="26">
@@ -10343,7 +11346,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.15</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="27">
@@ -10353,7 +11356,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21.99</v>
+        <v>71.67</v>
       </c>
     </row>
     <row r="28">
@@ -10363,7 +11366,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29">
